--- a/data/trans_dic/P6901-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P6901-Clase-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores en la espalda</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores en la espalda (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45,09; 70,17</t>
+          <t>45,37; 69,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,7; 76,16</t>
+          <t>51,22; 78,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,42; 70,16</t>
+          <t>38,84; 68,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31,24; 61,08</t>
+          <t>32,17; 60,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,07; 73,46</t>
+          <t>46,09; 73,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,15; 74,45</t>
+          <t>44,14; 75,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,76; 75,87</t>
+          <t>48,35; 75,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,34; 72,52</t>
+          <t>51,72; 72,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48,7; 68,81</t>
+          <t>49,03; 68,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51,37; 71,81</t>
+          <t>50,99; 71,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47,3; 68,52</t>
+          <t>46,44; 68,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,08; 64,19</t>
+          <t>45,53; 64,32</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,99; 66,75</t>
+          <t>35,95; 67,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56,85; 87,62</t>
+          <t>59,33; 89,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58,9; 89,77</t>
+          <t>59,85; 89,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40,83; 70,3</t>
+          <t>42,56; 70,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,04; 95,15</t>
+          <t>72,35; 93,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,34; 91,42</t>
+          <t>50,32; 91,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,36; 96,95</t>
+          <t>74,53; 96,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,88; 69,32</t>
+          <t>40,53; 69,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>56,28; 76,76</t>
+          <t>56,86; 77,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61,6; 85,82</t>
+          <t>61,39; 85,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72,78; 91,72</t>
+          <t>72,98; 91,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>45,75; 66,96</t>
+          <t>45,08; 66,33</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>71,5; 87,06</t>
+          <t>70,84; 86,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,52; 80,07</t>
+          <t>59,96; 80,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56,01; 80,36</t>
+          <t>55,75; 79,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56,29; 81,39</t>
+          <t>55,26; 80,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54,67; 94,06</t>
+          <t>53,35; 93,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77,02; 97,14</t>
+          <t>75,85; 97,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,9; 100,0</t>
+          <t>55,27; 100,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>62,13; 93,19</t>
+          <t>61,37; 93,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>72,15; 86,77</t>
+          <t>71,74; 86,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67,58; 83,5</t>
+          <t>67,95; 84,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58,94; 81,57</t>
+          <t>59,3; 81,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>60,94; 81,8</t>
+          <t>60,11; 81,36</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73,71; 84,79</t>
+          <t>74,04; 85,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,05; 84,51</t>
+          <t>67,89; 83,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,09; 85,54</t>
+          <t>71,38; 85,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75,54; 88,93</t>
+          <t>75,24; 88,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,24; 83,45</t>
+          <t>57,94; 83,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,91; 89,86</t>
+          <t>71,01; 89,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,67; 96,76</t>
+          <t>82,28; 96,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>71,38; 86,39</t>
+          <t>71,3; 85,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>73,77; 84,15</t>
+          <t>72,86; 83,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72,19; 83,8</t>
+          <t>72,18; 84,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78,32; 88,48</t>
+          <t>78,37; 88,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76,82; 86,19</t>
+          <t>76,89; 86,18</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>73,89; 92,59</t>
+          <t>73,01; 92,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,12; 94,77</t>
+          <t>70,6; 94,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,41; 91,25</t>
+          <t>73,27; 91,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74,32; 96,4</t>
+          <t>73,65; 96,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>80,45; 95,66</t>
+          <t>80,91; 95,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,57; 91,4</t>
+          <t>65,27; 91,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,69; 97,73</t>
+          <t>81,02; 97,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>76,24; 97,52</t>
+          <t>78,13; 97,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>80,31; 92,5</t>
+          <t>80,29; 92,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74,55; 91,46</t>
+          <t>73,71; 90,85</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79,17; 92,27</t>
+          <t>79,5; 92,85</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>80,3; 95,98</t>
+          <t>79,94; 95,57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1349,62 +1349,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,56%</t>
         </is>
       </c>
     </row>
@@ -1417,221 +1417,80 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>71,04; 78,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>69,39; 79,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>69,38; 78,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>67,47; 77,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>71,9; 83,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>71,63; 83,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>79,65; 89,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>73,1; 84,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>72,43; 78,97</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>71,76; 79,34</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>74,66; 81,88</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>71,64; 79,78</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>75,07%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>74,3%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>74,51%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>72,75%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>77,95%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>78,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>84,96%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>78,27%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>75,99%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>75,76%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>78,5%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>75,56%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>70,83; 78,8</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>69,29; 79,44</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>69,64; 79,32</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>67,51; 77,89</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>71,88; 83,08</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>71,79; 83,76</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>79,06; 88,9</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>72,58; 84,27</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>72,42; 79,35</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>71,98; 79,67</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>74,75; 82,01</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>71,79; 79,81</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
@@ -1647,7 +1506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1669,7 +1528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores en la espalda</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores en la espalda (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1786,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>29343; 45671</t>
+          <t>29526; 45222</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27562; 42238</t>
+          <t>28404; 43495</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18021; 32915</t>
+          <t>18221; 32012</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14314; 27983</t>
+          <t>14738; 27805</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21025; 34267</t>
+          <t>21500; 34426</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17993; 31048</t>
+          <t>18405; 31352</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21021; 34851</t>
+          <t>22208; 34508</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30438; 42995</t>
+          <t>30668; 42800</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54417; 76888</t>
+          <t>54778; 77023</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49907; 69770</t>
+          <t>49545; 69933</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43918; 63618</t>
+          <t>43119; 63811</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>49484; 67464</t>
+          <t>47860; 67602</t>
         </is>
       </c>
     </row>
@@ -2135,62 +1994,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14395; 28274</t>
+          <t>15226; 28655</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20659; 31843</t>
+          <t>21561; 32347</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17808; 27144</t>
+          <t>18095; 27116</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20731; 35696</t>
+          <t>21609; 35634</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29979; 39599</t>
+          <t>30109; 38768</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14197; 24331</t>
+          <t>13392; 24415</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21858; 28496</t>
+          <t>21906; 28506</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17235; 29223</t>
+          <t>17087; 29507</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47256; 64454</t>
+          <t>47743; 65293</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38784; 54026</t>
+          <t>38646; 53571</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43397; 54692</t>
+          <t>43518; 54527</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>42518; 62231</t>
+          <t>41893; 61646</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2202,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>71518; 87082</t>
+          <t>70861; 86676</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48060; 63582</t>
+          <t>47610; 63862</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37462; 53756</t>
+          <t>37290; 53024</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32941; 47634</t>
+          <t>32337; 47190</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8905; 15320</t>
+          <t>8689; 15302</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25971; 32756</t>
+          <t>25580; 32741</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5349; 9569</t>
+          <t>5289; 9569</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11084; 16624</t>
+          <t>10947; 16634</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>83927; 100931</t>
+          <t>83447; 100868</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>76453; 94459</t>
+          <t>76870; 95491</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45064; 62369</t>
+          <t>45343; 62208</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>46534; 62466</t>
+          <t>45904; 62129</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2410,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>148039; 170276</t>
+          <t>148687; 171588</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>80335; 98317</t>
+          <t>78990; 97244</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>97295; 117078</t>
+          <t>97694; 116712</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>100638; 118465</t>
+          <t>100230; 118437</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29088; 41680</t>
+          <t>28941; 41796</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48868; 61065</t>
+          <t>48256; 61097</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>68669; 81353</t>
+          <t>69178; 80919</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>75486; 91364</t>
+          <t>75406; 90585</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>184999; 211028</t>
+          <t>182705; 208512</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>133053; 154444</t>
+          <t>133023; 155397</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>173038; 195496</t>
+          <t>173164; 195287</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>183586; 205976</t>
+          <t>183738; 205959</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2618,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>47296; 59269</t>
+          <t>46732; 58966</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28452; 37914</t>
+          <t>28243; 37828</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50725; 63050</t>
+          <t>50628; 63545</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38029; 49328</t>
+          <t>37687; 49179</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>52796; 62775</t>
+          <t>53096; 62689</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29070; 39913</t>
+          <t>28500; 40008</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38184; 46252</t>
+          <t>38340; 46277</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>97008; 124087</t>
+          <t>99417; 123859</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>104104; 119915</t>
+          <t>104079; 119934</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62374; 76524</t>
+          <t>61677; 76017</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>92165; 107420</t>
+          <t>92551; 108097</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>143260; 171244</t>
+          <t>142634; 170505</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2831,62 +2690,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>334</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>241</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>248</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>167</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>152</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>176</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>373</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>501</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>386</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>417</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>621</t>
         </is>
       </c>
     </row>
@@ -2899,62 +2758,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>354578</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>243376</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>260795</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>171575</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166663</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>183756</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>275728</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>526154</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>410038</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>444551</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>522705</t>
         </is>
       </c>
     </row>
@@ -2967,282 +2826,74 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>335509; 372213</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>227282; 259495</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>242826; 274945</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>229067; 262543</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>158264; 183829</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>153048; 177544</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>172284; 193490</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>257515; 297636</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>501537; 546815</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>388400; 429377</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>422810; 463700</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>495623; 551911</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>386</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>354578</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>243376</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>260795</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>246977</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>171575</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>166663</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>183756</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>275728</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>526154</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>410038</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>444551</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>522705</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>334550; 372165</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>226963; 260196</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>243733; 277615</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>229201; 264426</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>158216; 182869</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>153383; 178952</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>171011; 192299</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>255683; 296872</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>501482; 549421</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>389548; 431185</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>423295; 464402</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>496619; 552093</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
@@ -3252,7 +2903,6 @@
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="K1:N1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P6901-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P6901-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>57,76%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45,37; 69,48</t>
+          <t>45,27; 69,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,22; 78,43</t>
+          <t>50,36; 78,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,84; 68,24</t>
+          <t>37,37; 69,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,17; 60,69</t>
+          <t>35,76; 65,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>46,09; 73,8</t>
+          <t>43,8; 73,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,14; 75,18</t>
+          <t>43,47; 73,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,35; 75,12</t>
+          <t>46,29; 75,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,72; 72,19</t>
+          <t>52,72; 72,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>49,03; 68,94</t>
+          <t>49,56; 68,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50,99; 71,98</t>
+          <t>52,67; 73,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46,44; 68,73</t>
+          <t>45,35; 68,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45,53; 64,32</t>
+          <t>48,31; 65,93</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,07%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,95; 67,65</t>
+          <t>34,82; 65,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59,33; 89,01</t>
+          <t>57,07; 88,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59,85; 89,68</t>
+          <t>57,98; 89,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42,56; 70,18</t>
+          <t>41,13; 70,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,35; 93,16</t>
+          <t>70,73; 93,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,32; 91,74</t>
+          <t>51,04; 91,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,53; 96,98</t>
+          <t>76,32; 96,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,53; 69,99</t>
+          <t>41,21; 68,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>56,86; 77,76</t>
+          <t>56,86; 76,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61,39; 85,09</t>
+          <t>60,55; 85,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72,98; 91,44</t>
+          <t>72,6; 91,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>45,08; 66,33</t>
+          <t>45,94; 65,71</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>73,91%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>70,84; 86,65</t>
+          <t>71,26; 86,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,96; 80,43</t>
+          <t>59,48; 80,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55,75; 79,27</t>
+          <t>56,25; 80,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55,26; 80,64</t>
+          <t>58,23; 82,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>53,35; 93,95</t>
+          <t>52,84; 93,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75,85; 97,09</t>
+          <t>76,96; 97,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,27; 100,0</t>
+          <t>56,1; 100,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>61,37; 93,25</t>
+          <t>61,76; 93,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>71,74; 86,72</t>
+          <t>71,96; 86,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67,95; 84,41</t>
+          <t>67,67; 83,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59,3; 81,36</t>
+          <t>60,15; 81,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>60,11; 81,36</t>
+          <t>64,4; 83,33</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>82,01%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,04; 85,44</t>
+          <t>74,41; 85,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67,89; 83,58</t>
+          <t>67,92; 83,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,38; 85,27</t>
+          <t>71,43; 85,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75,24; 88,9</t>
+          <t>76,72; 88,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,94; 83,68</t>
+          <t>58,42; 83,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,01; 89,91</t>
+          <t>70,68; 90,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,28; 96,24</t>
+          <t>82,16; 96,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>71,3; 85,65</t>
+          <t>72,53; 86,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>72,86; 83,15</t>
+          <t>73,07; 83,07</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72,18; 84,32</t>
+          <t>71,59; 84,39</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78,37; 88,39</t>
+          <t>78,14; 88,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76,89; 86,18</t>
+          <t>76,69; 86,39</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>73,01; 92,12</t>
+          <t>72,54; 92,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>70,6; 94,56</t>
+          <t>72,62; 94,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,27; 91,97</t>
+          <t>72,87; 91,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73,65; 96,11</t>
+          <t>80,03; 97,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>80,91; 95,53</t>
+          <t>81,91; 95,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,27; 91,62</t>
+          <t>67,16; 92,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,02; 97,79</t>
+          <t>80,54; 97,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>78,13; 97,34</t>
+          <t>88,12; 96,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>80,29; 92,52</t>
+          <t>80,82; 92,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73,71; 90,85</t>
+          <t>73,76; 91,14</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79,5; 92,85</t>
+          <t>78,6; 92,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>79,94; 95,57</t>
+          <t>87,62; 96,04</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>76,26%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,04; 78,81</t>
+          <t>70,82; 79,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69,39; 79,22</t>
+          <t>69,03; 78,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69,38; 78,56</t>
+          <t>69,24; 79,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>67,47; 77,33</t>
+          <t>69,95; 79,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>71,9; 83,51</t>
+          <t>72,29; 83,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71,63; 83,1</t>
+          <t>70,59; 83,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79,65; 89,46</t>
+          <t>79,3; 89,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>73,1; 84,49</t>
+          <t>73,64; 81,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>72,43; 78,97</t>
+          <t>72,44; 79,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71,76; 79,34</t>
+          <t>71,93; 79,27</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>74,66; 81,88</t>
+          <t>75,14; 82,04</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>71,64; 79,78</t>
+          <t>72,91; 79,25</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21244</t>
+          <t>26826</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37000</t>
+          <t>39060</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>58244</t>
+          <t>65886</t>
         </is>
       </c>
     </row>
@@ -1786,62 +1786,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>29526; 45222</t>
+          <t>29462; 45534</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28404; 43495</t>
+          <t>27929; 43350</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18221; 32012</t>
+          <t>17531; 32437</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14738; 27805</t>
+          <t>18609; 34065</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21500; 34426</t>
+          <t>20434; 34112</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18405; 31352</t>
+          <t>18127; 30831</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22208; 34508</t>
+          <t>21262; 34543</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30668; 42800</t>
+          <t>32705; 45104</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54778; 77023</t>
+          <t>55377; 76066</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49545; 69933</t>
+          <t>51175; 70939</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43119; 63811</t>
+          <t>42102; 63451</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>47860; 67602</t>
+          <t>55108; 75201</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28562</t>
+          <t>29098</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23643</t>
+          <t>25577</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52204</t>
+          <t>54675</t>
         </is>
       </c>
     </row>
@@ -1994,62 +1994,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15226; 28655</t>
+          <t>14747; 27824</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21561; 32347</t>
+          <t>20742; 32035</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18095; 27116</t>
+          <t>17532; 27132</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21609; 35634</t>
+          <t>21413; 36932</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30109; 38768</t>
+          <t>29435; 38709</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13392; 24415</t>
+          <t>13584; 24407</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21906; 28506</t>
+          <t>22434; 28501</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17087; 29507</t>
+          <t>18731; 31350</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47743; 65293</t>
+          <t>47742; 64583</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38646; 53571</t>
+          <t>38123; 53812</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43518; 54527</t>
+          <t>43294; 54730</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41893; 61646</t>
+          <t>44800; 64075</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40917</t>
+          <t>43912</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>16650</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>55259</t>
+          <t>60562</t>
         </is>
       </c>
     </row>
@@ -2202,62 +2202,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>70861; 86676</t>
+          <t>71277; 86903</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>47610; 63862</t>
+          <t>47230; 64034</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37290; 53024</t>
+          <t>37627; 53523</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32337; 47190</t>
+          <t>35806; 50856</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8689; 15302</t>
+          <t>8606; 15288</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25580; 32741</t>
+          <t>25952; 32737</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5289; 9569</t>
+          <t>5368; 9569</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10947; 16634</t>
+          <t>12634; 19051</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>83447; 100868</t>
+          <t>83704; 100843</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>76870; 95491</t>
+          <t>76547; 94278</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45343; 62208</t>
+          <t>45993; 62050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>45904; 62129</t>
+          <t>52769; 68283</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>110991</t>
+          <t>128623</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>84165</t>
+          <t>90780</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>195156</t>
+          <t>219403</t>
         </is>
       </c>
     </row>
@@ -2410,62 +2410,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>148687; 171588</t>
+          <t>149431; 171492</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>78990; 97244</t>
+          <t>79016; 97398</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>97694; 116712</t>
+          <t>97767; 117521</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>100230; 118437</t>
+          <t>117968; 136745</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28941; 41796</t>
+          <t>29181; 41579</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48256; 61097</t>
+          <t>48028; 61266</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>69178; 80919</t>
+          <t>69082; 81113</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>75406; 90585</t>
+          <t>82512; 98092</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182705; 208512</t>
+          <t>183239; 208307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>133023; 155397</t>
+          <t>131941; 155539</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>173164; 195287</t>
+          <t>172656; 196187</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>183738; 205959</t>
+          <t>205176; 231119</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45264</t>
+          <t>59735</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>116578</t>
+          <t>95200</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>161841</t>
+          <t>154935</t>
         </is>
       </c>
     </row>
@@ -2618,62 +2618,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>46732; 58966</t>
+          <t>46434; 59072</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28243; 37828</t>
+          <t>29052; 37871</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50628; 63545</t>
+          <t>50350; 63482</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37687; 49179</t>
+          <t>52550; 63810</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>53096; 62689</t>
+          <t>53750; 62842</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28500; 40008</t>
+          <t>29327; 40440</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38340; 46277</t>
+          <t>38114; 46273</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>99417; 123859</t>
+          <t>89580; 98593</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>104079; 119934</t>
+          <t>104774; 119783</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>61677; 76017</t>
+          <t>61719; 76257</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>92551; 108097</t>
+          <t>91509; 108089</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>142634; 170505</t>
+          <t>146601; 160699</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>246977</t>
+          <t>288195</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>275728</t>
+          <t>267268</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>522705</t>
+          <t>555462</t>
         </is>
       </c>
     </row>
@@ -2826,62 +2826,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>335509; 372213</t>
+          <t>334494; 373635</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>227282; 259495</t>
+          <t>226127; 258741</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>242826; 274945</t>
+          <t>242356; 277379</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>229067; 262543</t>
+          <t>269317; 304522</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>158264; 183829</t>
+          <t>159126; 183386</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>153048; 177544</t>
+          <t>150830; 178059</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>172284; 193490</t>
+          <t>171528; 194382</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>257515; 297636</t>
+          <t>252835; 281120</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>501537; 546815</t>
+          <t>501604; 547366</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>388400; 429377</t>
+          <t>389279; 428998</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>422810; 463700</t>
+          <t>425538; 464599</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>495623; 551911</t>
+          <t>531077; 577257</t>
         </is>
       </c>
     </row>
